--- a/jira_export_2026-08-12.xlsx
+++ b/jira_export_2026-08-12.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>144 h</t>
+          <t>147 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - GEODP PLACIER</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[Commune du Tampon] - Migration GEODP Placier</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1957,7 +1957,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3749,7 +3749,7 @@
         <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3821,7 +3821,7 @@
         <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>16</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
@@ -7804,12 +7804,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7842,14 +7842,14 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -7866,22 +7866,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7889,44 +7889,36 @@
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M101" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr"/>
       <c r="N101" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7936,22 +7928,22 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7959,7 +7951,7 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -7969,12 +7961,12 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
@@ -7985,16 +7977,16 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O102" s="16" t="n">
         <v>0</v>
@@ -8006,22 +7998,22 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8034,7 +8026,7 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -8044,21 +8036,29 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O103" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8068,22 +8068,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8106,25 +8106,17 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M104" s="14" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
       <c r="N104" s="15" t="n">
         <v>0</v>
       </c>
@@ -8138,12 +8130,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8153,7 +8145,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8166,7 +8158,7 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -8176,23 +8168,23 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
@@ -8208,22 +8200,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8236,33 +8228,33 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8278,28 +8270,26 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v/>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -8313,22 +8303,30 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L107" s="11" t="inlineStr"/>
-      <c r="M107" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N107" s="12" t="n">
         <v>0</v>
       </c>
@@ -8342,23 +8340,27 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C108" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8373,19 +8375,19 @@
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L108" s="14" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -8400,31 +8402,91 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="17" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr"/>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
+      <c r="N109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B109" s="17" t="inlineStr"/>
-      <c r="C109" s="17" t="inlineStr"/>
-      <c r="D109" s="17" t="inlineStr"/>
-      <c r="E109" s="17" t="inlineStr"/>
-      <c r="F109" s="17" t="inlineStr"/>
-      <c r="G109" s="17" t="inlineStr"/>
-      <c r="H109" s="17" t="inlineStr"/>
-      <c r="I109" s="17" t="inlineStr"/>
-      <c r="J109" s="17" t="inlineStr"/>
-      <c r="K109" s="17" t="inlineStr"/>
-      <c r="L109" s="17" t="inlineStr"/>
-      <c r="M109" s="17" t="inlineStr"/>
-      <c r="N109" s="18" t="n">
+      <c r="B110" s="17" t="inlineStr"/>
+      <c r="C110" s="17" t="inlineStr"/>
+      <c r="D110" s="17" t="inlineStr"/>
+      <c r="E110" s="17" t="inlineStr"/>
+      <c r="F110" s="17" t="inlineStr"/>
+      <c r="G110" s="17" t="inlineStr"/>
+      <c r="H110" s="17" t="inlineStr"/>
+      <c r="I110" s="17" t="inlineStr"/>
+      <c r="J110" s="17" t="inlineStr"/>
+      <c r="K110" s="17" t="inlineStr"/>
+      <c r="L110" s="17" t="inlineStr"/>
+      <c r="M110" s="17" t="inlineStr"/>
+      <c r="N110" s="18" t="n">
         <v>65373.694</v>
       </c>
-      <c r="O109" s="18" t="n">
+      <c r="O110" s="18" t="n">
         <v>1003.15</v>
       </c>
-      <c r="P109" s="18" t="n">
-        <v>12.42</v>
+      <c r="P110" s="18" t="n">
+        <v>12.05</v>
       </c>
     </row>
   </sheetData>
@@ -8534,6 +8596,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9108,16 +9171,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>64.75</v>
+        <v>66.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>78</v>
+        <v>80.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>20</v>
@@ -9127,7 +9190,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9201,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -9147,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -9157,7 +9220,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9232,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>43.25</v>
+        <v>43.75</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-12.xlsx
+++ b/jira_export_2026-08-12.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>147 h</t>
+          <t>153 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1957,7 +1957,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1616</v>
+        <v>4040</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -8480,13 +8480,13 @@
       <c r="L110" s="17" t="inlineStr"/>
       <c r="M110" s="17" t="inlineStr"/>
       <c r="N110" s="18" t="n">
-        <v>65373.694</v>
+        <v>67797.694</v>
       </c>
       <c r="O110" s="18" t="n">
         <v>1003.15</v>
       </c>
       <c r="P110" s="18" t="n">
-        <v>12.05</v>
+        <v>11.66</v>
       </c>
     </row>
   </sheetData>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>66.75</v>
+        <v>68.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>12.25</v>
@@ -9180,17 +9180,17 @@
         <v>1.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>80.25</v>
+        <v>81.75</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>43.75</v>
+        <v>44.75</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-12.xlsx
+++ b/jira_export_2026-08-12.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1,003 €</t>
+          <t>1,053 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>368 €</t>
+          <t>418 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>153 h</t>
+          <t>160 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P110"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1126,27 +1126,27 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34857</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Matching DA/DPA</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Matching DA/DPA</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1166,23 +1166,23 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J6" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34861</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>00177271</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N6" s="15" t="n">
@@ -1198,27 +1198,27 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheter par la CC</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -1238,17 +1238,25 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L7" s="11" t="inlineStr"/>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34929</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>00178034</t>
+        </is>
+      </c>
       <c r="N7" s="12" t="n">
         <v>0</v>
       </c>
@@ -1262,32 +1270,32 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34857</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[COMMUNE DE BIARRITZ] - Matching DA/DPA</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Matching DA/DPA</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1297,34 +1305,34 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34861</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00177271</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
-        <v>2419</v>
-      </c>
-      <c r="O8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="15" t="n">
@@ -1334,42 +1342,42 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34848</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Modification en-tête des arrêtés (1ère page uniquement) sur Littéralis</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -1381,22 +1389,14 @@
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34791</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>00177122</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
       <c r="N9" s="12" t="n">
-        <v>429.3</v>
-      </c>
-      <c r="O9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -1406,27 +1406,27 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
@@ -1457,16 +1457,16 @@
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>789.5</v>
+        <v>2419</v>
       </c>
       <c r="O10" s="16" t="n">
         <v>0</v>
@@ -1478,32 +1478,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1529,16 +1529,16 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>495</v>
+        <v>429.3</v>
       </c>
       <c r="O11" s="16" t="n">
         <v>0</v>
@@ -1550,32 +1550,32 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1585,32 +1585,32 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>1892</v>
+        <v>789.5</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,32 +1622,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1673,16 +1673,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>895</v>
+        <v>495</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1734,27 +1734,27 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>50</v>
+        <v>1892</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,27 +1766,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de La Flèche] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1806,27 +1806,27 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>769.5</v>
+        <v>895</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1838,27 +1838,27 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
@@ -1889,19 +1889,19 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O16" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O16" s="15" t="n">
+        <v>50</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>0</v>
@@ -1910,32 +1910,32 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1945,32 +1945,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>4536</v>
+        <v>769.5</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,27 +1982,27 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,19 +2033,19 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>525</v>
+        <v>2127.2</v>
       </c>
       <c r="O18" s="16" t="n">
-        <v>367.5</v>
+        <v>0</v>
       </c>
       <c r="P18" s="15" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1662</v>
+        <v>4536</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,42 +2126,42 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
@@ -2173,15 +2173,23 @@
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L20" s="14" t="inlineStr"/>
-      <c r="M20" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34216</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>00171155</t>
+        </is>
+      </c>
       <c r="N20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="15" t="n">
-        <v>0</v>
+        <v>525</v>
+      </c>
+      <c r="O20" s="16" t="n">
+        <v>367.5</v>
       </c>
       <c r="P20" s="15" t="n">
         <v>0</v>
@@ -2190,27 +2198,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2225,12 +2233,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2241,16 +2249,16 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2262,69 +2270,61 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34117</t>
-        </is>
-      </c>
-      <c r="M22" s="14" t="inlineStr">
-        <is>
-          <t>00170907</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L22" s="14" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
       <c r="N22" s="15" t="n">
-        <v>707</v>
-      </c>
-      <c r="O22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2334,12 +2334,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2369,32 +2369,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>300</v>
+        <v>9623.1</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2406,27 +2406,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
@@ -2457,16 +2457,16 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>510</v>
+        <v>707</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2478,32 +2478,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2518,27 +2518,27 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>5.5</v>
+        <v>0.25</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>242.9</v>
+        <v>300</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2550,32 +2550,32 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2601,16 +2601,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2622,32 +2622,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2657,34 +2657,34 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.25</v>
+        <v>5.5</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="12" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="O27" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -2694,32 +2694,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2745,16 +2745,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>680</v>
+        <v>220</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2766,32 +2766,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2801,34 +2801,34 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
@@ -2838,32 +2838,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2873,49 +2873,49 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="15" t="n">
-        <v>416.29</v>
+        <v>680</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>50.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2957,20 +2957,20 @@
         <v>2</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1890</v>
+        <v>787.5</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2982,27 +2982,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3022,64 +3022,64 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>920</v>
-      </c>
-      <c r="O32" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>416.29</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>0</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3089,32 +3089,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>4040</v>
+        <v>1890</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3126,32 +3126,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3177,16 +3177,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>1017.5</v>
+        <v>920</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3198,27 +3198,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3233,32 +3233,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1416</v>
+        <v>4040</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3270,32 +3270,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3310,27 +3310,27 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>171.4</v>
+        <v>1017.5</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3342,12 +3342,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3393,16 +3393,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>4174</v>
+        <v>1416</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3414,32 +3414,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3486,32 +3486,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3521,32 +3521,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>514.2</v>
+        <v>4174</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3558,27 +3558,27 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3609,16 +3609,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3630,32 +3630,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3665,32 +3665,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>149</v>
+        <v>514.2</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3702,32 +3702,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3774,32 +3774,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3809,34 +3809,34 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="O43" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
@@ -3846,32 +3846,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3881,32 +3881,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3918,32 +3918,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3953,34 +3953,34 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
@@ -3990,27 +3990,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4030,27 +4030,27 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>1079</v>
+        <v>910</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4062,32 +4062,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4113,16 +4113,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4134,27 +4134,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4174,27 +4174,27 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>400</v>
+        <v>1079</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4206,27 +4206,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4246,64 +4246,64 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1294.224</v>
+        <v>500</v>
       </c>
       <c r="O49" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>87.73999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4329,16 +4329,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>142.1</v>
+        <v>400</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4350,32 +4350,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4385,69 +4385,69 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>2335</v>
+        <v>1294.224</v>
       </c>
       <c r="O51" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>0</v>
+        <v>87.73999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4457,32 +4457,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>450</v>
+        <v>142.1</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4494,32 +4494,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4529,32 +4529,32 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>910</v>
+        <v>2335</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4566,23 +4566,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr"/>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4602,7 +4606,7 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4613,16 +4617,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>255</v>
+        <v>450</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4634,32 +4638,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4669,34 +4673,34 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
+        <v>910</v>
+      </c>
+      <c r="O55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4706,27 +4710,23 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr"/>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
@@ -4757,16 +4757,16 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4778,27 +4778,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4818,29 +4818,29 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4850,32 +4850,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4890,29 +4890,29 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4922,12 +4922,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4973,16 +4973,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4994,12 +4994,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5029,34 +5029,34 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5066,32 +5066,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
@@ -5117,16 +5117,16 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5138,32 +5138,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5189,16 +5189,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5210,32 +5210,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5245,32 +5245,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5282,27 +5282,27 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5322,27 +5322,27 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5354,32 +5354,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5389,32 +5389,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>700</v>
+        <v>203.5</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5426,61 +5426,69 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L66" s="14" t="inlineStr"/>
-      <c r="M66" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M66" s="14" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5490,27 +5498,27 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5530,27 +5538,27 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.5</v>
+        <v>5.75</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>416.475</v>
+        <v>700</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5562,69 +5570,61 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M68" s="14" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L68" s="14" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
       <c r="N68" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5634,32 +5634,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5669,32 +5669,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>281</v>
+        <v>416.475</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5706,12 +5706,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5721,12 +5721,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5757,16 +5757,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,12 +5778,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5829,16 +5829,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5850,12 +5850,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -5890,27 +5890,27 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5922,32 +5922,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>690</v>
+        <v>255</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5994,32 +5994,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6029,34 +6029,34 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6066,27 +6066,27 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6106,27 +6106,27 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.08</v>
+        <v>1.75</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6189,18 +6189,18 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6210,32 +6210,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6245,32 +6245,32 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>725</v>
+        <v>187.5</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6282,26 +6282,28 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -6315,34 +6317,34 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6352,32 +6354,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6387,34 +6389,34 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O79" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6424,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6439,13 +6441,11 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v/>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
@@ -6691,18 +6691,18 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6712,12 +6712,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6727,11 +6727,13 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6750,23 +6752,23 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6782,12 +6784,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6797,11 +6799,13 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -6820,27 +6824,27 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1212</v>
+        <v>1320</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6852,28 +6856,26 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v/>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -6892,23 +6894,23 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6924,12 +6926,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6939,13 +6941,11 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v/>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
@@ -6954,31 +6954,39 @@
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L87" s="11" t="inlineStr"/>
-      <c r="M87" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O87" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6988,12 +6996,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -7003,11 +7011,13 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -7026,23 +7036,23 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7058,26 +7068,28 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
@@ -7086,35 +7098,27 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L89" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27995</t>
-        </is>
-      </c>
-      <c r="M89" s="11" t="inlineStr">
-        <is>
-          <t>501218</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr"/>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
@@ -7128,22 +7132,22 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7166,23 +7170,23 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7198,22 +7202,22 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7236,23 +7240,23 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7283,7 +7287,7 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7313,16 +7317,16 @@
         <v>13</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
@@ -7383,16 +7387,16 @@
         <v>13</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
@@ -7408,22 +7412,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7441,34 +7445,34 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7478,12 +7482,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7493,7 +7497,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7509,20 +7513,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H95" s="11" t="inlineStr"/>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr"/>
-      <c r="M95" s="11" t="inlineStr"/>
+        <v>1.19</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7536,12 +7552,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7551,7 +7567,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7569,34 +7585,34 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7606,22 +7622,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7637,36 +7653,24 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H97" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H97" s="11" t="inlineStr"/>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M97" s="11" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr"/>
       <c r="N97" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7676,22 +7680,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7704,23 +7708,35 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H98" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L98" s="14" t="inlineStr"/>
-      <c r="M98" s="14" t="inlineStr"/>
+        <v>4.25</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N98" s="15" t="n">
         <v>0</v>
       </c>
@@ -7734,12 +7750,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7749,7 +7765,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7767,34 +7783,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O99" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7804,22 +7820,22 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7835,21 +7851,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H100" s="14" t="inlineStr"/>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -7866,12 +7878,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7881,7 +7893,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7894,7 +7906,7 @@
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
@@ -7904,17 +7916,25 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L101" s="11" t="inlineStr"/>
-      <c r="M101" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N101" s="12" t="n">
         <v>0</v>
       </c>
@@ -7928,22 +7948,22 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7951,44 +7971,36 @@
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M102" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
       <c r="N102" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -7998,12 +8010,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8013,7 +8025,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8026,39 +8038,31 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M103" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
       <c r="N103" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8068,22 +8072,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8091,36 +8095,44 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr"/>
-      <c r="M104" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M104" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8130,12 +8142,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8145,7 +8157,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8158,7 +8170,7 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -8168,29 +8180,29 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8200,22 +8212,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8228,7 +8240,7 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
@@ -8238,25 +8250,17 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M106" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
       <c r="N106" s="15" t="n">
         <v>0</v>
       </c>
@@ -8270,22 +8274,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8303,28 +8307,28 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
@@ -8340,28 +8344,26 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>Suresnes</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v/>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -8380,14 +8382,14 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="14" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -8404,24 +8406,26 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C109" s="11" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v/>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8430,63 +8434,265 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K109" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12666</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>19/09/2023</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K110" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M110" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
+      <c r="N111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr"/>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G112" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H112" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K112" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr"/>
-      <c r="N109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="17" t="inlineStr">
+      <c r="L112" s="14" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+      <c r="N112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B110" s="17" t="inlineStr"/>
-      <c r="C110" s="17" t="inlineStr"/>
-      <c r="D110" s="17" t="inlineStr"/>
-      <c r="E110" s="17" t="inlineStr"/>
-      <c r="F110" s="17" t="inlineStr"/>
-      <c r="G110" s="17" t="inlineStr"/>
-      <c r="H110" s="17" t="inlineStr"/>
-      <c r="I110" s="17" t="inlineStr"/>
-      <c r="J110" s="17" t="inlineStr"/>
-      <c r="K110" s="17" t="inlineStr"/>
-      <c r="L110" s="17" t="inlineStr"/>
-      <c r="M110" s="17" t="inlineStr"/>
-      <c r="N110" s="18" t="n">
-        <v>67797.694</v>
-      </c>
-      <c r="O110" s="18" t="n">
-        <v>1003.15</v>
-      </c>
-      <c r="P110" s="18" t="n">
-        <v>11.66</v>
+      <c r="B113" s="17" t="inlineStr"/>
+      <c r="C113" s="17" t="inlineStr"/>
+      <c r="D113" s="17" t="inlineStr"/>
+      <c r="E113" s="17" t="inlineStr"/>
+      <c r="F113" s="17" t="inlineStr"/>
+      <c r="G113" s="17" t="inlineStr"/>
+      <c r="H113" s="17" t="inlineStr"/>
+      <c r="I113" s="17" t="inlineStr"/>
+      <c r="J113" s="17" t="inlineStr"/>
+      <c r="K113" s="17" t="inlineStr"/>
+      <c r="L113" s="17" t="inlineStr"/>
+      <c r="M113" s="17" t="inlineStr"/>
+      <c r="N113" s="18" t="n">
+        <v>67747.694</v>
+      </c>
+      <c r="O113" s="18" t="n">
+        <v>1053.15</v>
+      </c>
+      <c r="P113" s="18" t="n">
+        <v>11.35</v>
       </c>
     </row>
   </sheetData>
@@ -8597,6 +8803,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9171,16 +9380,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>68.25</v>
+        <v>74</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>81.75</v>
+        <v>88.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>22</v>
@@ -9190,7 +9399,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9441,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>44.75</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -9317,10 +9526,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>389245</v>
+        <v>389195</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>146172</v>
+        <v>146122</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>243073</v>
@@ -9367,10 +9576,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>214534</v>
+        <v>214484</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>76165</v>
+        <v>76115</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>138370</v>
